--- a/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -5201,22 +5201,22 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Q6 accepts an answer sitting exactly on its stated maximum</t>
+          <t>Q6 blocks a blank answer</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 accepts an answer of exactly 500 characters. A maximum is a limit, so the limit itself is inside the rule. One more than this is already tested as a rejection; an off-by-one in the build sits precisely between the two.</t>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -5232,12 +5232,12 @@
       <c r="N30" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type a 500-character answer, then submit.</t>
+then: At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY (exactly at the limit)</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type a 500-character answer, then submit.</t>
+          <t>At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -5267,22 +5267,23 @@
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y30" s="6" t="inlineStr">
@@ -5313,7 +5314,7 @@
       </c>
       <c r="AD30" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE30" s="6" t="inlineStr">
@@ -5343,12 +5344,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -5358,22 +5359,22 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Q6 accepts punctuation and quotation marks</t>
+          <t>Q6 quotes the answer given at Q5</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 accepts an answer containing apostrophes, quotation marks and angle brackets. Its rule constrains length and says nothing about content, so this must be accepted. Quotes and brackets are where survey tools most often break, because nobody wrote the rule down and so nobody tested it.</t>
+          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -5389,12 +5390,12 @@
       <c r="N31" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>VALID_SPECIAL_CHARACTERS</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -5404,7 +5405,7 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -5434,7 +5435,7 @@
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q6's wording includes: Yes</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
@@ -5455,7 +5456,7 @@
       </c>
       <c r="AA31" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -5470,7 +5471,7 @@
       </c>
       <c r="AD31" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE31" s="6" t="inlineStr">
@@ -5500,12 +5501,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>9. Rule Interaction</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -5515,17 +5516,17 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Q6 refuses an answer of spaces alone</t>
+          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses an answer of spaces alone. The questionnaire marks it compulsory, and spaces are not an answer. This is the commoner real-world failure than a blank, because a respondent pressing the space bar looks like a respondent who answered.</t>
+          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -5546,12 +5547,12 @@
       <c r="N32" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type 3 spaces and nothing else, then submit.</t>
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>WHITESPACE_ONLY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
@@ -5561,17 +5562,17 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
@@ -5581,23 +5582,23 @@
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. Q6 is on screen
+2. Q6's wording includes: Yes</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y32" s="6" t="inlineStr">
@@ -5613,12 +5614,12 @@
       </c>
       <c r="AA32" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
-        </is>
-      </c>
-      <c r="AB32" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB32" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC32" s="8" t="inlineStr">
@@ -5628,12 +5629,12 @@
       </c>
       <c r="AD32" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE32" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5664,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -5673,22 +5674,22 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Q6 blocks a blank answer</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -5704,12 +5705,12 @@
       <c r="N33" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type nothing, then submit.</t>
+then: At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
@@ -5719,17 +5720,17 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type nothing, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
@@ -5739,23 +5740,22 @@
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y33" s="6" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -5831,22 +5831,22 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Q6 quotes the answer given at Q5</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -5862,7 +5862,7 @@
       <c r="N34" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>1. Q6's wording includes: Yes</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AA34" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB34" s="8" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AD34" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE34" s="6" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -5988,17 +5988,17 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
+          <t>Q6 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -6019,7 +6019,7 @@
       <c r="N35" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T35" s="6" t="inlineStr">
@@ -6054,23 +6054,23 @@
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. Q6's wording includes: Yes</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y35" s="6" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="AA35" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB35" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
+        </is>
+      </c>
+      <c r="AB35" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC35" s="8" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE35" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -6933,22 +6933,22 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts an answer sitting exactly on its stated maximum</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer of exactly 500 characters. A maximum is a limit, so the limit itself is inside the rule. One more than this is already tested as a rejection; an off-by-one in the build sits precisely between the two.</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -6964,12 +6964,12 @@
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 500-character answer, then submit.</t>
+then: At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY (exactly at the limit)</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 500-character answer, then submit.</t>
+          <t>At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="AD41" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE41" s="6" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts punctuation and quotation marks</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer containing apostrophes, quotation marks and angle brackets. Its rule constrains length and says nothing about content, so this must be accepted. Quotes and brackets are where survey tools most often break, because nobody wrote the rule down and so nobody tested it.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
@@ -7121,12 +7121,12 @@
       <c r="N42" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>VALID_SPECIAL_CHARACTERS</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -7247,22 +7247,22 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts spaces alone, being optional</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer of spaces alone. The questionnaire marks it optional, so nothing about the response may block progress.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -7278,12 +7278,12 @@
       <c r="N43" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type 3 spaces and nothing else, then submit.</t>
+then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>WHITESPACE_ONLY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
+          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -7347,9 +7347,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB43" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB43" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC43" s="8" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="AD43" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7435,12 +7435,12 @@
       <c r="N44" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type nothing, then submit.</t>
+then: At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P44" s="6" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type nothing, then submit.</t>
+          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -7504,9 +7504,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB44" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB44" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC44" s="8" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AE44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>

--- a/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -861,12 +861,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  -&gt;  COMPLETE</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  -&gt;  COMPLETE</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>12 test(s): TC-FT19, TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24 ...</t>
+          <t>12 test(s): TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24, TC-FT25 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8  -&gt;  COMPLETE</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8  -&gt;  COMPLETE</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>23 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
+          <t>24 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T5" s="6" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="U6" s="6" t="inlineStr">
         <is>
-          <t>S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T8" s="6" t="inlineStr">
@@ -1819,7 +1819,7 @@
       <c r="W8" s="6" t="inlineStr">
         <is>
           <t>1. S2 is on screen
-2. the next question shown is Q1</t>
+2. the next question shown is DT1</t>
         </is>
       </c>
       <c r="X8" s="6" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>DT1</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Q1 accepts a normal answer and the survey moves on</t>
+          <t>DT1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering DT1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q1.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as DT1.</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
+          <t>Every answer before DT1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T11" s="6" t="inlineStr">
@@ -2290,8 +2290,7 @@
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>1. Q1 is on screen
-2. the next question shown is Q2</t>
+          <t>1. the next question shown is Q1</t>
         </is>
       </c>
       <c r="X11" s="6" t="inlineStr">
@@ -2306,7 +2305,7 @@
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>Q1 | Which channel did you primarily use for this cafeteria visit? | single | Counter; Mobile pre-order; Vending kiosk | Always show</t>
+          <t>DT1 | Great, you're eligible for this survey! Next, a few quick questions about your recent cafeteria visit. | text display | — | Always show</t>
         </is>
       </c>
       <c r="AA11" s="6" t="inlineStr">
@@ -2356,12 +2355,12 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -2371,22 +2370,22 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Q1 blocks a blank answer</t>
+          <t>Q1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -2401,13 +2400,13 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes
-then: At Q1, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
@@ -2417,17 +2416,17 @@
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>At Q1, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1  (refused at Q1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -2437,23 +2436,23 @@
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q1</t>
+          <t>1. Q1 is on screen
+2. the next question shown is Q2</t>
         </is>
       </c>
       <c r="X12" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y12" s="6" t="inlineStr">
@@ -2483,7 +2482,7 @@
       </c>
       <c r="AD12" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE12" s="6" t="inlineStr">
@@ -2498,7 +2497,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -2513,12 +2512,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -2528,27 +2527,27 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Q2 accepts a normal answer and the survey moves on</t>
+          <t>Q1 blocks a blank answer</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q1.</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -2558,33 +2557,33 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes
+then: At Q1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
+          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1  (refused at Q1; respondent stays put)</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -2594,23 +2593,23 @@
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>1. Q2 is on screen
-2. the next question shown is Q3</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q1</t>
         </is>
       </c>
       <c r="X13" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y13" s="6" t="inlineStr">
@@ -2620,7 +2619,7 @@
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <t>Q2 | Overall, how satisfied were you with the cafeteria visit? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q1 | Which channel did you primarily use for this cafeteria visit? | single | Counter; Mobile pre-order; Vending kiosk | Always show</t>
         </is>
       </c>
       <c r="AA13" s="6" t="inlineStr">
@@ -2640,7 +2639,7 @@
       </c>
       <c r="AD13" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE13" s="6" t="inlineStr">
@@ -2670,12 +2669,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -2685,22 +2684,22 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Q2 blocks a blank answer</t>
+          <t>Q2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -2715,13 +2714,13 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter
-then: At Q2, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
@@ -2731,17 +2730,17 @@
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>At Q2, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2  (refused at Q2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -2751,23 +2750,23 @@
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q2</t>
+          <t>1. Q2 is on screen
+2. the next question shown is Q3</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y14" s="6" t="inlineStr">
@@ -2797,7 +2796,7 @@
       </c>
       <c r="AD14" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE14" s="6" t="inlineStr">
@@ -2812,7 +2811,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2827,12 +2826,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -2842,27 +2841,27 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Q3 accepts a normal answer and the survey moves on</t>
+          <t>Q2 blocks a blank answer</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q3.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -2872,33 +2871,33 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter
+then: At Q2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
+          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2  (refused at Q2; respondent stays put)</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -2908,23 +2907,23 @@
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>1. Q3 is on screen
-2. the next question shown is Q4_SQ001</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q2</t>
         </is>
       </c>
       <c r="X15" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y15" s="6" t="inlineStr">
@@ -2934,7 +2933,7 @@
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q2 | Overall, how satisfied were you with the cafeteria visit? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -2954,7 +2953,7 @@
       </c>
       <c r="AD15" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE15" s="6" t="inlineStr">
@@ -2984,12 +2983,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -2999,22 +2998,22 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Q3 blocks a blank answer</t>
+          <t>Q3 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -3029,13 +3028,13 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor
-then: At Q3, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
@@ -3045,17 +3044,17 @@
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>At Q3, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3  (refused at Q3; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -3065,23 +3064,23 @@
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
-          <t>Q4, Q5, Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q3</t>
+          <t>1. Q3 is on screen
+2. the next question shown is Q4_SQ001</t>
         </is>
       </c>
       <c r="X16" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y16" s="6" t="inlineStr">
@@ -3111,7 +3110,7 @@
       </c>
       <c r="AD16" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE16" s="6" t="inlineStr">
@@ -3126,7 +3125,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -3141,12 +3140,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -3156,27 +3155,27 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Q4 accepts a normal answer and the survey moves on</t>
+          <t>Q3 blocks a blank answer</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q3.</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -3186,33 +3185,33 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor
+then: At Q3, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
+          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q3, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3  (refused at Q3; respondent stays put)</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -3222,23 +3221,23 @@
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>1. Q4 is on screen
-2. the next question shown is Q5</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q3</t>
         </is>
       </c>
       <c r="X17" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y17" s="6" t="inlineStr">
@@ -3248,7 +3247,7 @@
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Food quality; Menu variety; Waiting time; Cleanliness; Staff behaviour; Price | Validate: {"min_selections": 1}</t>
+          <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA17" s="6" t="inlineStr">
@@ -3268,7 +3267,7 @@
       </c>
       <c r="AD17" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE17" s="6" t="inlineStr">
@@ -3298,7 +3297,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -3313,17 +3312,17 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Q4 accepts a valid answer</t>
+          <t>Q4 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 accepts an answer that obeys its stated rule. The rule is: at least 1 option must be selected</t>
+          <t>Prove that answering Q4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -3343,13 +3342,13 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor
-then: At Q4, tick 1 option (Food quality), then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
@@ -3359,17 +3358,17 @@
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>At Q4, tick 1 option (Food quality), then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -3389,7 +3388,8 @@
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q4 is on screen
+2. the next question shown is Q5</t>
         </is>
       </c>
       <c r="X18" s="6" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AD18" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE18" s="6" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Q4 rejects an invalid answer</t>
+          <t>Q4 accepts a valid answer</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 refuses an answer that breaks its stated rule. The rule is: at least 1 option must be selected</t>
+          <t>Prove Q4 accepts an answer that obeys its stated rule. The rule is: at least 1 option must be selected</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -3500,12 +3500,12 @@
       <c r="N19" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor
-then: At Q4, select nothing at all, then submit.</t>
+then: At Q4, tick 1 option (Food quality), then submit.</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
@@ -3515,17 +3515,17 @@
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>At Q4, select nothing at all, then submit.</t>
+          <t>At Q4, tick 1 option (Food quality), then submit.</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -3535,23 +3535,22 @@
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
-          <t>Q5, Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q4</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X19" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y19" s="6" t="inlineStr">
@@ -3626,22 +3625,22 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Q4 blocks a blank answer</t>
+          <t>Q4 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question.</t>
+          <t>Prove Q4 refuses an answer that breaks its stated rule. The rule is: at least 1 option must be selected</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -3662,7 +3661,7 @@
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
@@ -3677,12 +3676,12 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -3738,7 +3737,7 @@
       </c>
       <c r="AD20" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE20" s="6" t="inlineStr">
@@ -3753,7 +3752,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -3768,12 +3767,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -3783,27 +3782,27 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Q5 accepts a normal answer and the survey moves on</t>
+          <t>Q4 blocks a blank answer</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q5 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question.</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -3813,33 +3812,33 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor
+then: At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -3849,23 +3848,23 @@
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>1. Q5 is on screen
-2. the next question shown is Q6</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q4</t>
         </is>
       </c>
       <c r="X21" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y21" s="6" t="inlineStr">
@@ -3875,7 +3874,7 @@
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Food quality; Menu variety; Waiting time; Cleanliness; Staff behaviour; Price | Validate: {"min_selections": 1}</t>
         </is>
       </c>
       <c r="AA21" s="6" t="inlineStr">
@@ -3895,7 +3894,7 @@
       </c>
       <c r="AD21" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE21" s="6" t="inlineStr">
@@ -3940,12 +3939,12 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>R4 jumps forward when its condition is met</t>
+          <t>Q5 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Prove R4 jumps to Q7. The rule is: Q5 == 'No'</t>
+          <t>Prove that answering Q5 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -3970,8 +3969,8 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality
-then: At Q5, choose “No”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
@@ -3986,17 +3985,17 @@
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>At Q5, choose “No”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -4006,7 +4005,7 @@
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
@@ -4016,7 +4015,8 @@
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q7</t>
+          <t>1. Q5 is on screen
+2. the next question shown is Q6</t>
         </is>
       </c>
       <c r="X22" s="6" t="inlineStr">
@@ -4031,8 +4031,7 @@
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show
-Rules exercised: R4</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
         </is>
       </c>
       <c r="AA22" s="6" t="inlineStr">
@@ -4040,9 +4039,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB22" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB22" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC22" s="8" t="inlineStr">
@@ -4052,12 +4051,12 @@
       </c>
       <c r="AD22" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE22" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: rule_precedence</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4086,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -4097,12 +4096,12 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>R4 does not jump when its condition is not met</t>
+          <t>R4 jumps forward when its condition is met</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Prove R4 does not jump and the respondent continues in sequence. The rule is: Q5 == 'No'</t>
+          <t>Prove R4 jumps to Q7. The rule is: Q5 == 'No'</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -4128,7 +4127,7 @@
       <c r="N23" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality
-then: At Q5, choose “Yes”, then submit.</t>
+then: At Q5, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
@@ -4143,17 +4142,17 @@
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>At Q5, choose “Yes”, then submit.</t>
+          <t>At Q5, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -4163,7 +4162,7 @@
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
@@ -4173,7 +4172,7 @@
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q6</t>
+          <t>1. the next question shown is Q7</t>
         </is>
       </c>
       <c r="X23" s="6" t="inlineStr">
@@ -4197,9 +4196,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB23" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC23" s="8" t="inlineStr">
@@ -4214,7 +4213,7 @@
       </c>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: rule_precedence</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4238,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -4254,22 +4253,22 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Q5 blocks a blank answer</t>
+          <t>R4 does not jump when its condition is not met</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove R4 does not jump and the respondent continues in sequence. The rule is: Q5 == 'No'</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -4285,12 +4284,12 @@
       <c r="N24" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality
-then: At Q5, select nothing at all, then submit.</t>
+then: At Q5, choose “Yes”, then submit.</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
@@ -4300,17 +4299,17 @@
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>At Q5, select nothing at all, then submit.</t>
+          <t>At Q5, choose “Yes”, then submit.</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5  (refused at Q5; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -4320,23 +4319,22 @@
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q5</t>
+          <t>1. the next question shown is Q6</t>
         </is>
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y24" s="6" t="inlineStr">
@@ -4346,7 +4344,8 @@
       </c>
       <c r="Z24" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show
+Rules exercised: R4</t>
         </is>
       </c>
       <c r="AA24" s="6" t="inlineStr">
@@ -4366,7 +4365,7 @@
       </c>
       <c r="AD24" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE24" s="6" t="inlineStr">
@@ -4381,119 +4380,119 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT19</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Q5 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality
+then: At Q5, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>At Q5, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5  (refused at Q5; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT19</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Q6 accepts a normal answer and the survey moves on</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Prove that answering Q6 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T25" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. the next question shown is Q7</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q5</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y25" s="6" t="inlineStr">
@@ -4503,13 +4502,12 @@
       </c>
       <c r="Z25" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
         </is>
       </c>
       <c r="AA25" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -4524,7 +4522,7 @@
       </c>
       <c r="AD25" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE25" s="6" t="inlineStr">
@@ -4569,12 +4567,12 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown when its condition is met</t>
+          <t>Q6 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 IS shown when its display rule is satisfied. The rule is: Q5 == 'Yes'</t>
+          <t>Prove that answering Q6 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -4599,8 +4597,8 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -4615,17 +4613,17 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -4645,7 +4643,8 @@
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen</t>
+          <t>1. Q6 is on screen
+2. the next question shown is Q7</t>
         </is>
       </c>
       <c r="X26" s="6" t="inlineStr">
@@ -4661,8 +4660,7 @@
       <c r="Z26" s="6" t="inlineStr">
         <is>
           <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}
-Rules exercised: R3</t>
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA26" s="6" t="inlineStr">
@@ -4682,7 +4680,7 @@
       </c>
       <c r="AD26" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE26" s="6" t="inlineStr">
@@ -4717,7 +4715,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -4727,12 +4725,12 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Q6 is not shown when its condition is not met</t>
+          <t>Q6 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is NOT shown when its display rule is not satisfied. The rule is: Q5 == 'Yes'</t>
+          <t>Prove Q6 IS shown when its display rule is satisfied. The rule is: Q5 == 'Yes'</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -4757,13 +4755,13 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = No
-then: After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
@@ -4773,17 +4771,17 @@
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T27" s="6" t="inlineStr">
@@ -4793,7 +4791,7 @@
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V27" s="6" t="inlineStr">
@@ -4803,8 +4801,7 @@
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. Q6 is on screen</t>
         </is>
       </c>
       <c r="X27" s="6" t="inlineStr">
@@ -4829,9 +4826,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB27" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB27" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC27" s="8" t="inlineStr">
@@ -4841,12 +4838,12 @@
       </c>
       <c r="AD27" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE27" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: rule_precedence</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4871,12 +4868,12 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -4886,17 +4883,17 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Q6 accepts a valid answer</t>
+          <t>Q6 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 accepts an answer that obeys its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
+          <t>Prove Q6 is NOT shown when its display rule is not satisfied. The rule is: Q5 == 'Yes'</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -4916,13 +4913,13 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = No
+then: After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
@@ -4932,17 +4929,17 @@
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -4952,7 +4949,7 @@
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
@@ -4962,7 +4959,8 @@
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q6 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X28" s="6" t="inlineStr">
@@ -4978,7 +4976,8 @@
       <c r="Z28" s="6" t="inlineStr">
         <is>
           <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+Validate: {"min_length": 10, "max_length": 500}
+Rules exercised: R3</t>
         </is>
       </c>
       <c r="AA28" s="6" t="inlineStr">
@@ -4986,9 +4985,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB28" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB28" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC28" s="8" t="inlineStr">
@@ -4998,12 +4997,12 @@
       </c>
       <c r="AD28" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE28" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: rule_precedence</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5032,7 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -5043,12 +5042,12 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Q6 rejects an invalid answer</t>
+          <t>Q6 accepts a valid answer</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
+          <t>Prove Q6 accepts an answer that obeys its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -5074,12 +5073,12 @@
       <c r="N29" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type a 501-character answer, then submit.</t>
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
@@ -5089,17 +5088,17 @@
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type a 501-character answer, then submit.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -5109,23 +5108,22 @@
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y29" s="6" t="inlineStr">
@@ -5201,22 +5199,22 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Q6 blocks a blank answer</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -5232,12 +5230,12 @@
       <c r="N30" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type nothing, then submit.</t>
+then: At Q6, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
@@ -5247,17 +5245,17 @@
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type nothing, then submit.</t>
+          <t>At Q6, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -5314,7 +5312,7 @@
       </c>
       <c r="AD30" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE30" s="6" t="inlineStr">
@@ -5344,12 +5342,12 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -5359,17 +5357,17 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Q6 quotes the answer given at Q5</t>
+          <t>Q6 blocks a blank answer</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -5390,12 +5388,12 @@
       <c r="N31" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -5405,17 +5403,17 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -5425,22 +5423,23 @@
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>1. Q6's wording includes: Yes</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y31" s="6" t="inlineStr">
@@ -5456,7 +5455,7 @@
       </c>
       <c r="AA31" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -5471,7 +5470,7 @@
       </c>
       <c r="AD31" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE31" s="6" t="inlineStr">
@@ -5501,12 +5500,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>3. Dependency / Piping</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -5516,17 +5515,17 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
+          <t>Q6 quotes the answer given at Q5</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -5567,12 +5566,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S32" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T32" s="6" t="inlineStr">
@@ -5592,8 +5591,7 @@
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. Q6's wording includes: Yes</t>
+          <t>1. Q6's wording includes: Yes</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
@@ -5659,12 +5657,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>9. Rule Interaction</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -5674,22 +5672,22 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Q6 rejects an invalid answer</t>
+          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
+          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -5705,7 +5703,7 @@
       <c r="N33" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type a 500-character answer, then submit.</t>
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -5720,17 +5718,17 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type a 500-character answer, then submit.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
@@ -5750,7 +5748,8 @@
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q6 is on screen
+2. Q6's wording includes: Yes</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
@@ -5771,7 +5770,7 @@
       </c>
       <c r="AA33" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5786,7 +5785,7 @@
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
@@ -5862,7 +5861,7 @@
       <c r="N34" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -5877,17 +5876,17 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -5988,22 +5987,22 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Q6 allows a blank answer, being optional</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
@@ -6019,7 +6018,7 @@
       <c r="N35" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type 3 spaces and nothing else, then submit.</t>
+then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
@@ -6034,17 +6033,17 @@
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S35" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T35" s="6" t="inlineStr">
@@ -6054,23 +6053,22 @@
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y35" s="6" t="inlineStr">
@@ -6089,9 +6087,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB35" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB35" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC35" s="8" t="inlineStr">
@@ -6101,12 +6099,12 @@
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE35" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6114,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -6131,7 +6129,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -6141,32 +6139,32 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a normal answer and the survey moves on</t>
+          <t>Q6 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M36" s="6" t="inlineStr">
@@ -6176,8 +6174,8 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
+then: At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
@@ -6187,48 +6185,48 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S36" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 is on screen
-2. the next question shown is Q8</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X36" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y36" s="6" t="inlineStr">
@@ -6238,17 +6236,18 @@
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA36" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB36" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
+        </is>
+      </c>
+      <c r="AB36" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC36" s="8" t="inlineStr">
@@ -6258,12 +6257,12 @@
       </c>
       <c r="AD36" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE36" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6287,12 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -6303,22 +6302,22 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Q7 blocks a blank answer</t>
+          <t>Q7 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -6333,13 +6332,13 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx
-then: At Q7, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -6349,17 +6348,17 @@
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
@@ -6369,23 +6368,23 @@
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. Q7 is on screen
+2. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y37" s="6" t="inlineStr">
@@ -6415,7 +6414,7 @@
       </c>
       <c r="AD37" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE37" s="6" t="inlineStr">
@@ -6430,119 +6429,119 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT32</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Q7 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx
+then: At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U38" s="6" t="inlineStr">
+        <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT32</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Q8 accepts a normal answer and the survey moves on</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S38" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T38" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U38" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y38" s="6" t="inlineStr">
@@ -6552,8 +6551,7 @@
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA38" s="6" t="inlineStr">
@@ -6573,7 +6571,7 @@
       </c>
       <c r="AD38" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE38" s="6" t="inlineStr">
@@ -6603,7 +6601,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -6618,17 +6616,17 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a valid answer</t>
+          <t>Q8 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -6649,12 +6647,12 @@
       <c r="N39" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “x”, then submit.</t>
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -6664,17 +6662,17 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “x”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T39" s="6" t="inlineStr">
@@ -6694,7 +6692,8 @@
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q8 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X39" s="6" t="inlineStr">
@@ -6730,7 +6729,7 @@
       </c>
       <c r="AD39" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE39" s="6" t="inlineStr">
@@ -6765,7 +6764,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -6775,12 +6774,12 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>Q8 accepts a valid answer</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
@@ -6806,12 +6805,12 @@
       <c r="N40" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 501-character answer, then submit.</t>
+then: At Q8, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
@@ -6821,17 +6820,17 @@
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 501-character answer, then submit.</t>
+          <t>At Q8, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S40" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
@@ -6846,18 +6845,17 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X40" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y40" s="6" t="inlineStr">
@@ -6923,7 +6921,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -6933,22 +6931,22 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Q8 allows a blank answer, being optional</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -6964,12 +6962,12 @@
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type nothing, then submit.</t>
+then: At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -6979,17 +6977,17 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type nothing, then submit.</t>
+          <t>At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T41" s="6" t="inlineStr">
@@ -7004,17 +7002,18 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y41" s="6" t="inlineStr">
@@ -7045,7 +7044,7 @@
       </c>
       <c r="AD41" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE41" s="6" t="inlineStr">
@@ -7090,22 +7089,22 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -7121,12 +7120,12 @@
       <c r="N42" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 500-character answer, then submit.</t>
+then: At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
@@ -7136,17 +7135,17 @@
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 500-character answer, then submit.</t>
+          <t>At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S42" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
@@ -7202,7 +7201,7 @@
       </c>
       <c r="AD42" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE42" s="6" t="inlineStr">
@@ -7278,7 +7277,7 @@
       <c r="N43" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+then: At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
@@ -7293,17 +7292,17 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
+          <t>At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S43" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T43" s="6" t="inlineStr">
@@ -7404,22 +7403,22 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Q8 allows a blank answer, being optional</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
@@ -7435,7 +7434,7 @@
       <c r="N44" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type 3 spaces and nothing else, then submit.</t>
+then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr">
@@ -7450,17 +7449,17 @@
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
+          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S44" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T44" s="6" t="inlineStr">
@@ -7504,9 +7503,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB44" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB44" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC44" s="8" t="inlineStr">
@@ -7516,12 +7515,12 @@
       </c>
       <c r="AD44" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE44" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7531,151 +7530,308 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT39</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Q8 allows a blank answer, being optional</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>VALID_TYPICAL for every answer</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
+        </is>
+      </c>
+      <c r="W45" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
+        </is>
+      </c>
+      <c r="X45" s="6" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="Y45" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z45" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA45" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB45" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="AC45" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD45" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE45" s="6" t="inlineStr">
+        <is>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
           <t>whole survey</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>TC-RT03</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>ROUTE</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>6. Termination / Disposition</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>1. Flow / Routing</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>P03</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
-      <c r="J45" s="6" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr">
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>FRESH_RESPONDENT</t>
         </is>
       </c>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="N46" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O45" s="6" t="inlineStr">
+      <c r="O46" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P45" s="6" t="inlineStr">
+      <c r="P46" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S45" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T45" s="6" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T46" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U45" s="6" t="inlineStr">
+      <c r="U46" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V45" s="6" t="inlineStr">
+      <c r="V46" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W45" s="6" t="inlineStr">
+      <c r="W46" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X45" s="6" t="inlineStr">
+      <c r="X46" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y45" s="6" t="inlineStr">
+      <c r="Y46" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z45" s="6" t="inlineStr">
+      <c r="Z46" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA45" s="6" t="inlineStr">
+      <c r="AA46" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB45" s="8" t="inlineStr">
+      <c r="AB46" s="8" t="inlineStr">
         <is>
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="AC45" s="8" t="inlineStr">
+      <c r="AC46" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD45" s="6" t="inlineStr">
+      <c r="AD46" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE45" s="6" t="inlineStr">
+      <c r="AE46" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/S01_campus_cafeteria_experience/agent3/agent3_test_cases_with_paths.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>12 test(s): TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24, TC-FT25 ...</t>
+          <t>10 test(s): TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24, TC-FT25 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -5515,22 +5515,22 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Q6 quotes the answer given at Q5</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -5546,7 +5546,7 @@
       <c r="N32" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>1. Q6's wording includes: Yes</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AA32" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB32" s="8" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AD32" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE32" s="6" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -5672,22 +5672,22 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -5703,7 +5703,7 @@
       <c r="N33" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -5748,8 +5748,7 @@
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. Q6's wording includes: Yes</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
@@ -5770,7 +5769,7 @@
       </c>
       <c r="AA33" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5785,7 +5784,7 @@
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
@@ -5830,22 +5829,22 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Q6 rejects an invalid answer</t>
+          <t>Q6 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
+          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -5861,7 +5860,7 @@
       <c r="N34" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type a 500-character answer, then submit.</t>
+then: At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -5876,17 +5875,17 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type a 500-character answer, then submit.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -5896,22 +5895,23 @@
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y34" s="6" t="inlineStr">
@@ -5930,9 +5930,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB34" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB34" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC34" s="8" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AD34" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE34" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -5957,105 +5957,105 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT29</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>1. Flow / Routing</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Q7 accepts a normal answer and the survey moves on</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>VALID_TYPICAL for every answer</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT29</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>Q6 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T35" s="6" t="inlineStr">
+      <c r="U35" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -6063,7 +6063,8 @@
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q7 is on screen
+2. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
@@ -6078,13 +6079,12 @@
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA35" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE35" s="6" t="inlineStr">
@@ -6114,155 +6114,154 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT30</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Q7 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx
+then: At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT30</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="V36" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W36" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
+        </is>
+      </c>
+      <c r="X36" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y36" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z36" s="6" t="inlineStr">
+        <is>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+        </is>
+      </c>
+      <c r="AA36" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB36" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC36" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD36" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE36" s="6" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>Q6 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes
-then: At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
-        </is>
-      </c>
-      <c r="T36" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>Q7, Q8</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
-        <is>
-          <t>No forward navigation - the same question must reappear.</t>
-        </is>
-      </c>
-      <c r="W36" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
-        </is>
-      </c>
-      <c r="X36" s="6" t="inlineStr">
-        <is>
-          <t>Not reached - the respondent cannot progress</t>
-        </is>
-      </c>
-      <c r="Y36" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z36" s="6" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
-        </is>
-      </c>
-      <c r="AB36" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC36" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD36" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE36" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6271,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -6302,12 +6301,12 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a normal answer and the survey moves on</t>
+          <t>Q8 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -6322,7 +6321,7 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -6343,7 +6342,7 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
@@ -6378,8 +6377,8 @@
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 is on screen
-2. the next question shown is Q8</t>
+          <t>1. Q8 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
@@ -6394,7 +6393,8 @@
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA37" s="6" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -6459,27 +6459,27 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Q7 blocks a blank answer</t>
+          <t>Q8 accepts a valid answer</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -6489,33 +6489,33 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx
-then: At Q7, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>At Q8, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T38" s="6" t="inlineStr">
@@ -6525,23 +6525,22 @@
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y38" s="6" t="inlineStr">
@@ -6551,7 +6550,8 @@
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA38" s="6" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AD38" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE38" s="6" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a normal answer and the survey moves on</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -6647,12 +6647,12 @@
       <c r="N39" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -6687,18 +6687,18 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
         </is>
       </c>
       <c r="X39" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y39" s="6" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AD39" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE39" s="6" t="inlineStr">
@@ -6774,22 +6774,22 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a valid answer</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -6805,12 +6805,12 @@
       <c r="N40" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “x”, then submit.</t>
+then: At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “x”, then submit.</t>
+          <t>At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AD40" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE40" s="6" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -6962,12 +6962,12 @@
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 501-character answer, then submit.</t>
+then: At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 501-character answer, then submit.</t>
+          <t>At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
@@ -7002,18 +7002,17 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y41" s="6" t="inlineStr">
@@ -7089,22 +7088,22 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Q8 allows a blank answer, being optional</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -7120,12 +7119,12 @@
       <c r="N42" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type nothing, then submit.</t>
+then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
@@ -7135,7 +7134,7 @@
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type nothing, then submit.</t>
+          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -7201,7 +7200,7 @@
       </c>
       <c r="AD42" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE42" s="6" t="inlineStr">
@@ -7246,22 +7245,22 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -7277,7 +7276,7 @@
       <c r="N43" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 500-character answer, then submit.</t>
+then: At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
@@ -7292,7 +7291,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 500-character answer, then submit.</t>
+          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -7346,9 +7345,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB43" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB43" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC43" s="8" t="inlineStr">
@@ -7358,12 +7357,12 @@
       </c>
       <c r="AD43" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -7373,57 +7372,57 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>TC-FT38</t>
+          <t>TC-RT03</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -7432,406 +7431,92 @@
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S44" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T44" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U44" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V44" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W44" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X44" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y44" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z44" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA44" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB44" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="AC44" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD44" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE44" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT39</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Q8 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S45" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T45" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U45" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V45" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W45" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y45" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z45" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB45" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC45" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD45" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE45" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT03</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Counter; Q2 = Very poor; Q3 = Very poor; Q4 = Food quality; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O46" s="6" t="inlineStr">
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P46" s="6" t="inlineStr">
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
-      <c r="S46" s="6" t="inlineStr">
+      <c r="S44" s="6" t="inlineStr">
         <is>
           <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
-      <c r="T46" s="6" t="inlineStr">
+      <c r="T44" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U46" s="6" t="inlineStr">
+      <c r="U44" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V46" s="6" t="inlineStr">
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W46" s="6" t="inlineStr">
+      <c r="W44" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X46" s="6" t="inlineStr">
+      <c r="X44" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y46" s="6" t="inlineStr">
+      <c r="Y44" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z46" s="6" t="inlineStr">
+      <c r="Z44" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA46" s="6" t="inlineStr">
+      <c r="AA44" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB46" s="8" t="inlineStr">
+      <c r="AB44" s="8" t="inlineStr">
         <is>
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="AC46" s="8" t="inlineStr">
+      <c r="AC44" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD46" s="6" t="inlineStr">
+      <c r="AD44" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE46" s="6" t="inlineStr">
+      <c r="AE44" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
